--- a/haleon/haleon-설문원시데이터-더미.xlsx
+++ b/haleon/haleon-설문원시데이터-더미.xlsx
@@ -470,7 +470,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[일부러 심어 둔 지저분함 — 1교시 시연 3에서 정리합니다]</t>
+          <t>[일부러 심어 둔 지저분함 — 1교시 실습 4에서 정리합니다]</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>자세한 절차는 학습사이트 → 교시별 학습자료 → 1교시 Excel → 시연 3 을 보세요.</t>
+          <t>자세한 절차는 학습사이트 → 교시별 학습자료 → 1교시 Excel → 실습 4 를 보세요.</t>
         </is>
       </c>
     </row>

--- a/haleon/haleon-설문원시데이터-더미.xlsx
+++ b/haleon/haleon-설문원시데이터-더미.xlsx
@@ -525,7 +525,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>자세한 절차는 학습사이트 → 교시별 학습자료 → 1교시 Excel → 실습 4 를 보세요.</t>
+          <t>자세한 절차는 학습사이트 상단 메뉴 [1교시] → 실습 4 를 보세요.</t>
         </is>
       </c>
     </row>
